--- a/artfynd/A 13848-2021 artfynd.xlsx
+++ b/artfynd/A 13848-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 13848-2021 artfynd.xlsx
+++ b/artfynd/A 13848-2021 artfynd.xlsx
@@ -1042,7 +1042,7 @@
         <v>76488475</v>
       </c>
       <c r="B5" t="n">
-        <v>108203</v>
+        <v>110571</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430439.4580746571</v>
+        <v>430439</v>
       </c>
       <c r="R5" t="n">
-        <v>6478723.997521686</v>
+        <v>6478724</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1112,19 +1112,9 @@
           <t>2012-05-31</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2012-05-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
